--- a/www/flightdata/xlsx/eoss-362.xlsx
+++ b/www/flightdata/xlsx/eoss-362.xlsx
@@ -3390,7 +3390,7 @@
         <v>30171.24</v>
       </c>
       <c r="I2">
-        <v>649</v>
+        <v>428</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
